--- a/data/trans_bre/IP18_E_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP18_E_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,87</t>
+          <t>-3,55; 2,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,58</t>
+          <t>-1,57; 2,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,56</t>
+          <t>-5,37; 3,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-44,9; 0,0</t>
+          <t>-32,27; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,96</t>
+          <t>-3,55; 2,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,66</t>
+          <t>-1,57; 2,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 3,68</t>
+          <t>-5,41; 3,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,9; 0,0</t>
+          <t>-32,27; 0,0</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,57</t>
+          <t>-2,44; 2,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,99</t>
+          <t>-2,63; 1,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,15</t>
+          <t>-2,74; 1,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,46; -3,87</t>
+          <t>-26,18; -4,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,72</t>
+          <t>-2,55; 2,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,09</t>
+          <t>-2,72; 2,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 1,2</t>
+          <t>-2,81; 1,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,53; -4,09</t>
+          <t>-27,39; -4,59</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 10,46</t>
+          <t>-2,64; 10,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 6,29</t>
+          <t>-5,43; 5,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 6,89</t>
+          <t>-5,11; 6,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 13,04</t>
+          <t>-21,56; 13,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 13,32</t>
+          <t>-3,07; 13,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 7,37</t>
+          <t>-5,97; 6,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,3</t>
+          <t>-5,7; 8,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 18,5</t>
+          <t>-24,12; 18,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,91</t>
+          <t>-1,62; 2,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,83</t>
+          <t>-2,14; 2,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,1</t>
+          <t>-2,12; 1,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -3,42</t>
+          <t>-20,47; -2,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,14</t>
+          <t>-1,72; 3,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,95</t>
+          <t>-2,23; 2,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,25</t>
+          <t>-2,22; 2,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,78; -3,7</t>
+          <t>-21,14; -3,23</t>
         </is>
       </c>
     </row>
